--- a/data/significance-p-values-and-errors--battery_life.xlsx
+++ b/data/significance-p-values-and-errors--battery_life.xlsx
@@ -1893,7 +1893,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WHAT IS CAPTURED: a sample of batteries run down under standard load.</t>
+          <t>WHAT IS CAPTURED: a sample of batteries run down under standard load (a realistic teaching dataset written for the book).</t>
         </is>
       </c>
     </row>
